--- a/tea_inventory - 2025.xlsx
+++ b/tea_inventory - 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\工作\Code\Tea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD76E84-0DAF-48C8-9310-BDB52D890ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D90D918-73A2-4EF5-87DA-A6AA7B694B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1403,7 +1403,7 @@
         <v>36</v>
       </c>
       <c r="L10" s="1">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N10" s="1">
         <v>2025</v>
